--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R4" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,6 +984,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R5" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,11 +1096,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96362</v>
+        <v>96365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96269</v>
+        <v>96295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96365</v>
+        <v>96391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96391</v>
+        <v>96392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96296</v>
+        <v>96297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96392</v>
+        <v>96393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96393</v>
+        <v>96395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96299</v>
+        <v>96303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96395</v>
+        <v>96399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B4" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R4" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,11 +984,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R5" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,6 +1091,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R4" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,6 +984,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R5" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,11 +1096,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96303</v>
+        <v>96316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B4" t="n">
-        <v>97203</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R4" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,11 +984,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>97216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R5" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,6 +1091,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96399</v>
+        <v>96412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96316</v>
+        <v>96317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>97217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R4" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,6 +984,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>98971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R5" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,11 +1096,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96412</v>
+        <v>96413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343398</v>
       </c>
       <c r="B2" t="n">
-        <v>96317</v>
+        <v>96320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343396</v>
       </c>
       <c r="B3" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130343397</v>
       </c>
       <c r="B6" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130343393</v>
       </c>
       <c r="B7" t="n">
-        <v>96413</v>
+        <v>96416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B4" t="n">
-        <v>97220</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R4" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,11 +984,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>97220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R5" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,6 +1091,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343399</v>
+        <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>97220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628173</v>
+        <v>628153</v>
       </c>
       <c r="R4" t="n">
-        <v>6690284</v>
+        <v>6690261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,6 +984,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343400</v>
+        <v>130343399</v>
       </c>
       <c r="B5" t="n">
-        <v>97220</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628153</v>
+        <v>628173</v>
       </c>
       <c r="R5" t="n">
-        <v>6690261</v>
+        <v>6690284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,11 +1096,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130343398</v>
+        <v>130343395</v>
       </c>
       <c r="B2" t="n">
-        <v>96320</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628169</v>
+        <v>628214</v>
       </c>
       <c r="R2" t="n">
-        <v>6690292</v>
+        <v>6690263</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130343396</v>
+        <v>130343397</v>
       </c>
       <c r="B3" t="n">
-        <v>101163</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628187</v>
+        <v>628169</v>
       </c>
       <c r="R3" t="n">
-        <v>6690310</v>
+        <v>6690292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,6 +877,11 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,7 +902,7 @@
         <v>130343400</v>
       </c>
       <c r="B4" t="n">
-        <v>97220</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130343399</v>
+        <v>130343392</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628173</v>
+        <v>628287</v>
       </c>
       <c r="R5" t="n">
-        <v>6690284</v>
+        <v>6690217</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1113,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130343397</v>
+        <v>130343393</v>
       </c>
       <c r="B6" t="n">
-        <v>97220</v>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628169</v>
+        <v>628253</v>
       </c>
       <c r="R6" t="n">
-        <v>6690292</v>
+        <v>6690250</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,12 +1212,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>äldre barrsumpskog</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>murken granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130343393</v>
+        <v>130343398</v>
       </c>
       <c r="B7" t="n">
-        <v>96416</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628253</v>
+        <v>628169</v>
       </c>
       <c r="R7" t="n">
-        <v>6690250</v>
+        <v>6690292</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,12 +1324,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>äldre barrsumpskog</t>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>murken granlåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1334,6 +1344,449 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130343391</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628254</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6690089</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130343394</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628207</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6690250</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130343399</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628173</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6690284</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130343396</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628187</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6690310</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20997-2022 artfynd.xlsx
+++ b/artfynd/A 20997-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343395</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343397</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343391</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343394</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343399</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,8 +1837,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>